--- a/data/trans_bre/DCD-Edad-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,28</t>
+          <t>1,51; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,14</t>
+          <t>1,3; 4,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 21,31</t>
+          <t>8,93; 21,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,64; 1042,92</t>
+          <t>43,9; 1260,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,7; —</t>
+          <t>57,25; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>157,84; 3336,5</t>
+          <t>182,57; 4233,69</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,69</t>
+          <t>1,71; 6,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,25</t>
+          <t>1,04; 6,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 12,16</t>
+          <t>2,25; 12,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,66; 372,87</t>
+          <t>43,53; 340,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,84; 329,12</t>
+          <t>22,09; 299,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 375,88</t>
+          <t>32,52; 376,14</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,72</t>
+          <t>4,44; 10,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 7,79</t>
+          <t>2,52; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 11,84</t>
+          <t>3,76; 11,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80,6; 315,09</t>
+          <t>73,89; 319,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,01; 294,97</t>
+          <t>49,38; 302,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,67; 195,06</t>
+          <t>41,7; 205,52</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,52</t>
+          <t>4,43; 11,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,64</t>
+          <t>3,15; 9,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 21,0</t>
+          <t>8,17; 21,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,44; 232,19</t>
+          <t>51,8; 230,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 186,79</t>
+          <t>39,48; 204,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,29; 476,28</t>
+          <t>55,68; 405,0</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,99; 17,6</t>
+          <t>7,77; 17,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,47</t>
+          <t>0,8; 10,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 16,28</t>
+          <t>7,14; 15,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,81; 265,49</t>
+          <t>71,93; 269,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 105,01</t>
+          <t>4,86; 105,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,52; 92,35</t>
+          <t>30,98; 89,82</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 19,19</t>
+          <t>6,46; 20,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 12,53</t>
+          <t>1,76; 12,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 16,34</t>
+          <t>-9,91; 16,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32,18; 154,94</t>
+          <t>33,46; 167,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 170,54</t>
+          <t>15,28; 178,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 94,47</t>
+          <t>-50,86; 93,34</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,92; 25,08</t>
+          <t>9,59; 25,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 16,26</t>
+          <t>2,46; 15,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,97; 26,16</t>
+          <t>14,65; 26,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43,29; 159,27</t>
+          <t>36,97; 150,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 99,71</t>
+          <t>10,41; 93,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,0; 96,86</t>
+          <t>42,25; 100,29</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,18</t>
+          <t>8,17; 11,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,76</t>
+          <t>5,04; 8,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,79</t>
+          <t>7,34; 14,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111,66; 184,5</t>
+          <t>109,54; 185,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,08; 129,65</t>
+          <t>67,15; 133,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,93; 144,25</t>
+          <t>64,03; 146,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DCD-Edad-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,27</t>
+          <t>15,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>791,83%</t>
+          <t>888,42%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,11</t>
+          <t>1,48; 6,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,95</t>
+          <t>1,44; 4,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,93; 21,22</t>
+          <t>9,69; 21,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,9; 1260,71</t>
+          <t>49,37; 1248,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,25; —</t>
+          <t>72,82; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>182,57; 4233,69</t>
+          <t>240,53; 5186,23</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>162,51%</t>
+          <t>177,69%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,62</t>
+          <t>1,58; 6,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,07</t>
+          <t>1,1; 6,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 12,27</t>
+          <t>4,66; 13,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,53; 340,16</t>
+          <t>34,81; 352,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 299,28</t>
+          <t>21,93; 346,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,52; 376,14</t>
+          <t>60,75; 408,43</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>10,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>107,95%</t>
+          <t>154,49%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,45</t>
+          <t>4,32; 10,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,09</t>
+          <t>2,3; 7,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,99</t>
+          <t>7,1; 13,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,89; 319,35</t>
+          <t>72,7; 318,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,38; 302,55</t>
+          <t>42,77; 279,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,7; 205,52</t>
+          <t>74,42; 257,65</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>11,07</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>134,09%</t>
+          <t>81,42%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,74</t>
+          <t>4,2; 11,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,92</t>
+          <t>3,11; 9,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,17; 21,56</t>
+          <t>7,17; 14,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,8; 230,24</t>
+          <t>47,24; 226,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>39,48; 204,56</t>
+          <t>37,08; 192,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,68; 405,0</t>
+          <t>44,73; 123,68</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,52</t>
+          <t>11,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 17,78</t>
+          <t>7,64; 17,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,39</t>
+          <t>1,34; 10,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 15,81</t>
+          <t>7,95; 15,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,93; 269,58</t>
+          <t>69,65; 262,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 105,03</t>
+          <t>8,25; 106,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,98; 89,82</t>
+          <t>36,11; 92,93</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>15,62</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,46; 20,23</t>
+          <t>6,57; 20,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,47</t>
+          <t>2,2; 12,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 16,31</t>
+          <t>10,95; 20,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33,46; 167,31</t>
+          <t>34,04; 171,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,28; 178,75</t>
+          <t>15,68; 174,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,86; 93,34</t>
+          <t>51,63; 129,75</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,47</t>
+          <t>20,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,59; 25,13</t>
+          <t>10,86; 25,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,68</t>
+          <t>1,91; 15,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 26,23</t>
+          <t>15,6; 25,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36,97; 150,06</t>
+          <t>43,49; 161,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,41; 93,78</t>
+          <t>8,15; 94,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,25; 100,29</t>
+          <t>47,16; 96,11</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>107,38%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,22</t>
+          <t>8,13; 11,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,16</t>
+          <t>4,82; 7,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,75</t>
+          <t>12,25; 15,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109,54; 185,27</t>
+          <t>111,63; 186,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,15; 133,07</t>
+          <t>64,34; 125,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,03; 146,16</t>
+          <t>88,52; 130,46</t>
         </is>
       </c>
     </row>
